--- a/review-results/复盘信息抓取-20260903.xlsx
+++ b/review-results/复盘信息抓取-20260903.xlsx
@@ -1112,9 +1112,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>392.11</v>
+      </c>
       <c r="I2" s="3" t="n"/>
       <c r="L2" t="n">
         <v>1</v>
@@ -1136,9 +1152,25 @@
       <c r="T2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>395.89</v>
+      </c>
       <c r="I3" s="3" t="n"/>
       <c r="L3" t="n">
         <v>2</v>
@@ -1160,9 +1192,25 @@
       <c r="T3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>403.39</v>
+      </c>
       <c r="I4" s="3" t="n"/>
       <c r="L4" t="n">
         <v>3</v>
@@ -1184,9 +1232,25 @@
       <c r="T4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>414.36</v>
+      </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="L5" t="n">
@@ -1209,9 +1273,25 @@
       <c r="T5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>423.64</v>
+      </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="L6" t="n">
@@ -1234,9 +1314,25 @@
       <c r="T6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>405.29</v>
+      </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="L7" t="n">
@@ -1259,9 +1355,25 @@
       <c r="T7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>402.11</v>
+      </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="L8" t="n">
@@ -1284,9 +1396,25 @@
       <c r="T8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>395.97</v>
+      </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="L9" t="n">
@@ -1309,9 +1437,25 @@
       <c r="T9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>414.17</v>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="L10" t="n">
@@ -1334,9 +1478,25 @@
       <c r="T10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>419.38</v>
+      </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="L11" t="n">
@@ -1359,9 +1519,25 @@
       <c r="T11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>415.42</v>
+      </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="L12" t="n">
@@ -1384,9 +1560,25 @@
       <c r="T12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>414.36</v>
+      </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="L13" t="n">
@@ -1409,9 +1601,25 @@
       <c r="T13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>404.23</v>
+      </c>
       <c r="I14" s="3" t="n"/>
       <c r="L14" t="n">
         <v>13</v>
@@ -1433,9 +1641,25 @@
       <c r="T14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>395.41</v>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="L15" t="n">
         <v>14</v>
@@ -1457,9 +1681,25 @@
       <c r="T15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>402.41</v>
+      </c>
       <c r="I16" s="3" t="n"/>
       <c r="L16" t="n">
         <v>15</v>
@@ -1481,9 +1721,25 @@
       <c r="T16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>403.39</v>
+      </c>
       <c r="I17" s="3" t="n"/>
       <c r="L17" t="n">
         <v>16</v>
@@ -1505,9 +1761,25 @@
       <c r="T17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0415</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>394.67</v>
+      </c>
       <c r="I18" s="3" t="n"/>
       <c r="L18" t="n">
         <v>17</v>
@@ -1529,9 +1801,25 @@
       <c r="T18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>394.45</v>
+      </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="L19" t="n">
@@ -1554,9 +1842,25 @@
       <c r="T19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>393.98</v>
+      </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="L20" t="n">
@@ -1579,9 +1883,25 @@
       <c r="T20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>394.67</v>
+      </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="L21" t="n">
@@ -1604,9 +1924,25 @@
       <c r="T21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>387.92</v>
+      </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="L22" t="n">
@@ -1629,9 +1965,25 @@
       <c r="T22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>386.79</v>
+      </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="L23" t="n">
@@ -1654,9 +2006,25 @@
       <c r="T23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>404.23</v>
+      </c>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="L24" t="n">
@@ -1679,9 +2047,25 @@
       <c r="T24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>404.72</v>
+      </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="L25" t="n">
@@ -1704,9 +2088,25 @@
       <c r="T25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0615</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>416.45</v>
+      </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="L26" t="n">
@@ -1729,9 +2129,25 @@
       <c r="T26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>405.36</v>
+      </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="L27" t="n">
@@ -1754,9 +2170,25 @@
       <c r="T27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0645</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>404.98</v>
+      </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="L28" t="n">
@@ -1779,9 +2211,25 @@
       <c r="T28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>404.23</v>
+      </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="L29" t="n">
@@ -1804,9 +2252,25 @@
       <c r="T29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>417.25</v>
+      </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="L30" t="n">
@@ -1829,9 +2293,25 @@
       <c r="T30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>417.95</v>
+      </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="L31" t="n">
@@ -1854,9 +2334,25 @@
       <c r="T31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>404.72</v>
+      </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
       <c r="L32" t="n">
@@ -1879,9 +2375,25 @@
       <c r="T32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>392.8</v>
+      </c>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="L33" t="n">
@@ -1904,9 +2416,25 @@
       <c r="T33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0815</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>383.92</v>
+      </c>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="L34" t="n">
@@ -1929,9 +2457,25 @@
       <c r="T34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>367.11</v>
+      </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="L35" t="n">
@@ -1954,9 +2498,25 @@
       <c r="T35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>350.76</v>
+      </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="L36" t="n">
@@ -1979,9 +2539,25 @@
       <c r="T36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>349.42</v>
+      </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="L37" t="n">
@@ -2004,9 +2580,25 @@
       <c r="T37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>357.47</v>
+      </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="L38" t="n">
@@ -2029,9 +2621,25 @@
       <c r="T38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>350</v>
+      </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="L39" t="n">
@@ -2054,9 +2662,25 @@
       <c r="T39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>348.01</v>
+      </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="L40" t="n">
@@ -2079,9 +2703,25 @@
       <c r="T40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>348.57</v>
+      </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="L41" t="n">
@@ -2104,9 +2744,25 @@
       <c r="T41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>347.95</v>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="L42" t="n">
@@ -2129,9 +2785,25 @@
       <c r="T42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>349.42</v>
+      </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="L43" t="n">
@@ -2154,9 +2826,25 @@
       <c r="T43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>347.17</v>
+      </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="L44" t="n">
@@ -2179,9 +2867,25 @@
       <c r="T44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>347.47</v>
+      </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="L45" t="n">
@@ -2204,9 +2908,25 @@
       <c r="T45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>347.47</v>
+      </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="L46" t="n">
@@ -2229,9 +2949,25 @@
       <c r="T46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>360.14</v>
+      </c>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="L47" t="n">
@@ -2254,9 +2990,25 @@
       <c r="T47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>348.25</v>
+      </c>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="L48" t="n">
@@ -2279,9 +3031,25 @@
       <c r="T48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>353.76</v>
+      </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="L49" t="n">
@@ -2304,9 +3072,25 @@
       <c r="T49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>346.95</v>
+      </c>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="L50" t="n">
@@ -2329,9 +3113,25 @@
       <c r="T50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>348.25</v>
+      </c>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="L51" t="n">
@@ -2354,9 +3154,25 @@
       <c r="T51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>348.51</v>
+      </c>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="L52" t="n">
@@ -2379,9 +3195,25 @@
       <c r="T52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>349.42</v>
+      </c>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="L53" t="n">
@@ -2404,9 +3236,25 @@
       <c r="T53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>350.76</v>
+      </c>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="L54" t="n">
@@ -2429,9 +3277,25 @@
       <c r="T54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>350.76</v>
+      </c>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="L55" t="n">
@@ -2454,9 +3318,25 @@
       <c r="T55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>349.72</v>
+      </c>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="L56" t="n">
@@ -2479,9 +3359,25 @@
       <c r="T56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>348.57</v>
+      </c>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="L57" t="n">
@@ -2504,9 +3400,25 @@
       <c r="T57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>346.89</v>
+      </c>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="L58" t="n">
@@ -2529,9 +3441,25 @@
       <c r="T58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>357.89</v>
+      </c>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="L59" t="n">
@@ -2554,9 +3482,25 @@
       <c r="T59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>349.95</v>
+      </c>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="L60" t="n">
@@ -2579,9 +3523,25 @@
       <c r="T60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>358.92</v>
+      </c>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="L61" t="n">
@@ -2604,9 +3564,25 @@
       <c r="T61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>358.19</v>
+      </c>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="L62" t="n">
@@ -2629,9 +3605,25 @@
       <c r="T62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>350</v>
+      </c>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="L63" t="n">
@@ -2654,9 +3646,25 @@
       <c r="T63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>377.44</v>
+      </c>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
       <c r="L64" t="n">
@@ -2679,9 +3687,25 @@
       <c r="T64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>377.44</v>
+      </c>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="L65" t="n">
@@ -2704,9 +3728,25 @@
       <c r="T65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>423.51</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>375.42</v>
+      </c>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="L66" t="n">
@@ -2729,9 +3769,25 @@
       <c r="T66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>423.51</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>384.11</v>
+      </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
       <c r="L67" t="n">
@@ -2754,9 +3810,25 @@
       <c r="T67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>423.51</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>386.01</v>
+      </c>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="L68" t="n">
@@ -2779,9 +3851,25 @@
       <c r="T68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>423.51</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>375.51</v>
+      </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="L69" t="n">
@@ -2804,9 +3892,25 @@
       <c r="T69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>394.45</v>
+      </c>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="L70" t="n">
@@ -2829,9 +3933,25 @@
       <c r="T70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>403.39</v>
+      </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="L71" t="n">
@@ -2854,9 +3974,25 @@
       <c r="T71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>403.42</v>
+      </c>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="L72" t="n">
@@ -2879,9 +4015,25 @@
       <c r="T72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>415.07</v>
+      </c>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="L73" t="n">
@@ -2904,9 +4056,25 @@
       <c r="T73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>417.66</v>
+      </c>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="L74" t="n">
@@ -2929,9 +4097,25 @@
       <c r="T74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>424.2</v>
+      </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="L75" t="n">
@@ -2954,9 +4138,25 @@
       <c r="T75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>424.76</v>
+      </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="L76" t="n">
@@ -2979,9 +4179,25 @@
       <c r="T76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>424.85</v>
+      </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="L77" t="n">
@@ -3004,9 +4220,25 @@
       <c r="T77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>424.98</v>
+      </c>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="L78" t="n">
@@ -3029,9 +4261,25 @@
       <c r="T78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>424.76</v>
+      </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="L79" t="n">
@@ -3054,9 +4302,25 @@
       <c r="T79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>424.98</v>
+      </c>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="L80" t="n">
@@ -3079,9 +4343,25 @@
       <c r="T80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>417.95</v>
+      </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="L81" t="n">
@@ -3104,9 +4384,25 @@
       <c r="T81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>414.58</v>
+      </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="L82" t="n">
@@ -3129,9 +4425,25 @@
       <c r="T82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>414.36</v>
+      </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="L83" t="n">
@@ -3154,9 +4466,25 @@
       <c r="T83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>415.83</v>
+      </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="L84" t="n">
@@ -3179,9 +4507,25 @@
       <c r="T84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>404.58</v>
+      </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="L85" t="n">
@@ -3204,9 +4548,25 @@
       <c r="T85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>394.45</v>
+      </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
       <c r="L86" t="n">
@@ -3229,9 +4589,25 @@
       <c r="T86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>396.05</v>
+      </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="L87" t="n">
@@ -3254,9 +4630,25 @@
       <c r="T87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>403.42</v>
+      </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="L88" t="n">
@@ -3279,9 +4671,25 @@
       <c r="T88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>402.45</v>
+      </c>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="L89" t="n">
@@ -3304,9 +4712,25 @@
       <c r="T89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>395.41</v>
+      </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="L90" t="n">
@@ -3329,9 +4753,25 @@
       <c r="T90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>403.39</v>
+      </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
       <c r="L91" t="n">
@@ -3354,9 +4794,25 @@
       <c r="T91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>393.91</v>
+      </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="L92" t="n">
@@ -3379,9 +4835,25 @@
       <c r="T92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>404.66</v>
+      </c>
       <c r="I93" s="3" t="n"/>
       <c r="L93" t="n">
         <v>92</v>
@@ -3403,9 +4875,25 @@
       <c r="T93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>414.82</v>
+      </c>
       <c r="I94" s="3" t="n"/>
       <c r="L94" t="n">
         <v>93</v>
@@ -3427,9 +4915,25 @@
       <c r="T94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>414.58</v>
+      </c>
       <c r="I95" s="3" t="n"/>
       <c r="L95" t="n">
         <v>94</v>
@@ -3451,9 +4955,25 @@
       <c r="T95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>404.98</v>
+      </c>
       <c r="I96" s="3" t="n"/>
       <c r="L96" t="n">
         <v>95</v>
@@ -3475,9 +4995,25 @@
       <c r="T96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>405.29</v>
+      </c>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="L97" t="n">
@@ -4866,14 +6402,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
-      <c r="V2" s="3" t="n"/>
-      <c r="W2" s="3" t="n"/>
-      <c r="X2" s="3" t="n"/>
-      <c r="Y2" s="3" t="n"/>
-      <c r="Z2" s="3" t="n"/>
-      <c r="AA2" s="3" t="n"/>
-      <c r="AB2" s="3" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4936,14 +6498,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="3" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5006,14 +6594,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" s="3" t="n"/>
-      <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="3" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5076,14 +6690,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5146,14 +6786,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="3" t="n"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5216,14 +6882,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="n"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5286,14 +6978,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
-      <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="3" t="n"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5356,14 +7074,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="3" t="n"/>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5426,14 +7170,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5496,14 +7266,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="n"/>
-      <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="3" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5566,14 +7362,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="3" t="n"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5636,14 +7458,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5706,14 +7554,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5776,14 +7650,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5846,14 +7746,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5916,14 +7842,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="3" t="n"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5986,14 +7938,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="3" t="n"/>
-      <c r="AB18" s="3" t="n"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6056,14 +8034,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
-      <c r="Y19" s="3" t="n"/>
-      <c r="Z19" s="3" t="n"/>
-      <c r="AA19" s="3" t="n"/>
-      <c r="AB19" s="3" t="n"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6126,14 +8130,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="3" t="n"/>
-      <c r="Z20" s="3" t="n"/>
-      <c r="AA20" s="3" t="n"/>
-      <c r="AB20" s="3" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6196,14 +8226,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" s="3" t="n"/>
-      <c r="AA21" s="3" t="n"/>
-      <c r="AB21" s="3" t="n"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6266,14 +8322,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U22" s="3" t="n"/>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
-      <c r="Y22" s="3" t="n"/>
-      <c r="Z22" s="3" t="n"/>
-      <c r="AA22" s="3" t="n"/>
-      <c r="AB22" s="3" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6336,14 +8418,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="3" t="n"/>
-      <c r="AA23" s="3" t="n"/>
-      <c r="AB23" s="3" t="n"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6406,14 +8514,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="3" t="n"/>
-      <c r="Z24" s="3" t="n"/>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" s="3" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6476,14 +8610,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6546,14 +8706,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6616,14 +8802,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6686,14 +8898,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
-      <c r="AA28" s="3" t="n"/>
-      <c r="AB28" s="3" t="n"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6756,14 +8994,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
-      <c r="AA29" s="3" t="n"/>
-      <c r="AB29" s="3" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6826,14 +9090,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="3" t="n"/>
-      <c r="AB30" s="3" t="n"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6896,14 +9186,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U31" s="3" t="n"/>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
-      <c r="Y31" s="3" t="n"/>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6966,14 +9282,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7036,14 +9378,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
-      <c r="Y33" s="3" t="n"/>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7106,14 +9474,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" s="3" t="n"/>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="3" t="n"/>
-      <c r="AB34" s="3" t="n"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7176,14 +9570,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="3" t="n"/>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" s="3" t="n"/>
-      <c r="AA35" s="3" t="n"/>
-      <c r="AB35" s="3" t="n"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7246,14 +9666,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U36" s="3" t="n"/>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
-      <c r="Z36" s="3" t="n"/>
-      <c r="AA36" s="3" t="n"/>
-      <c r="AB36" s="3" t="n"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7316,14 +9762,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U37" s="3" t="n"/>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
-      <c r="Y37" s="3" t="n"/>
-      <c r="Z37" s="3" t="n"/>
-      <c r="AA37" s="3" t="n"/>
-      <c r="AB37" s="3" t="n"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB37" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7386,14 +9858,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U38" s="3" t="n"/>
-      <c r="V38" s="3" t="n"/>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
-      <c r="AA38" s="3" t="n"/>
-      <c r="AB38" s="3" t="n"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB38" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7456,14 +9954,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U39" s="3" t="n"/>
-      <c r="V39" s="3" t="n"/>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="n"/>
-      <c r="AA39" s="3" t="n"/>
-      <c r="AB39" s="3" t="n"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7526,14 +10050,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" s="3" t="n"/>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="3" t="n"/>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
-      <c r="AA40" s="3" t="n"/>
-      <c r="AB40" s="3" t="n"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7596,14 +10146,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U41" s="3" t="n"/>
-      <c r="V41" s="3" t="n"/>
-      <c r="W41" s="3" t="n"/>
-      <c r="X41" s="3" t="n"/>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n"/>
-      <c r="AA41" s="3" t="n"/>
-      <c r="AB41" s="3" t="n"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7666,14 +10242,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" s="3" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
-      <c r="AA42" s="3" t="n"/>
-      <c r="AB42" s="3" t="n"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7736,14 +10338,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
-      <c r="Y43" s="3" t="n"/>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" s="3" t="n"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7806,14 +10434,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" s="3" t="n"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7876,14 +10530,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U45" s="3" t="n"/>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7946,14 +10626,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
-      <c r="AA46" s="3" t="n"/>
-      <c r="AB46" s="3" t="n"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB46" s="3" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8016,14 +10722,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U47" s="3" t="n"/>
-      <c r="V47" s="3" t="n"/>
-      <c r="W47" s="3" t="n"/>
-      <c r="X47" s="3" t="n"/>
-      <c r="Y47" s="3" t="n"/>
-      <c r="Z47" s="3" t="n"/>
-      <c r="AA47" s="3" t="n"/>
-      <c r="AB47" s="3" t="n"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8086,14 +10818,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U48" s="3" t="n"/>
-      <c r="V48" s="3" t="n"/>
-      <c r="W48" s="3" t="n"/>
-      <c r="X48" s="3" t="n"/>
-      <c r="Y48" s="3" t="n"/>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="3" t="n"/>
-      <c r="AB48" s="3" t="n"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8156,14 +10914,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U49" s="3" t="n"/>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
-      <c r="Y49" s="3" t="n"/>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8226,14 +11010,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U50" s="3" t="n"/>
-      <c r="V50" s="3" t="n"/>
-      <c r="W50" s="3" t="n"/>
-      <c r="X50" s="3" t="n"/>
-      <c r="Y50" s="3" t="n"/>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
-      <c r="AB50" s="3" t="n"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8296,14 +11106,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U51" s="3" t="n"/>
-      <c r="V51" s="3" t="n"/>
-      <c r="W51" s="3" t="n"/>
-      <c r="X51" s="3" t="n"/>
-      <c r="Y51" s="3" t="n"/>
-      <c r="Z51" s="3" t="n"/>
-      <c r="AA51" s="3" t="n"/>
-      <c r="AB51" s="3" t="n"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8366,14 +11202,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U52" s="3" t="n"/>
-      <c r="V52" s="3" t="n"/>
-      <c r="W52" s="3" t="n"/>
-      <c r="X52" s="3" t="n"/>
-      <c r="Y52" s="3" t="n"/>
-      <c r="Z52" s="3" t="n"/>
-      <c r="AA52" s="3" t="n"/>
-      <c r="AB52" s="3" t="n"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB52" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8436,14 +11298,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U53" s="3" t="n"/>
-      <c r="V53" s="3" t="n"/>
-      <c r="W53" s="3" t="n"/>
-      <c r="X53" s="3" t="n"/>
-      <c r="Y53" s="3" t="n"/>
-      <c r="Z53" s="3" t="n"/>
-      <c r="AA53" s="3" t="n"/>
-      <c r="AB53" s="3" t="n"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8506,14 +11394,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U54" s="3" t="n"/>
-      <c r="V54" s="3" t="n"/>
-      <c r="W54" s="3" t="n"/>
-      <c r="X54" s="3" t="n"/>
-      <c r="Y54" s="3" t="n"/>
-      <c r="Z54" s="3" t="n"/>
-      <c r="AA54" s="3" t="n"/>
-      <c r="AB54" s="3" t="n"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8576,14 +11490,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U55" s="3" t="n"/>
-      <c r="V55" s="3" t="n"/>
-      <c r="W55" s="3" t="n"/>
-      <c r="X55" s="3" t="n"/>
-      <c r="Y55" s="3" t="n"/>
-      <c r="Z55" s="3" t="n"/>
-      <c r="AA55" s="3" t="n"/>
-      <c r="AB55" s="3" t="n"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8646,14 +11586,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U56" s="3" t="n"/>
-      <c r="V56" s="3" t="n"/>
-      <c r="W56" s="3" t="n"/>
-      <c r="X56" s="3" t="n"/>
-      <c r="Y56" s="3" t="n"/>
-      <c r="Z56" s="3" t="n"/>
-      <c r="AA56" s="3" t="n"/>
-      <c r="AB56" s="3" t="n"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8716,14 +11682,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U57" s="3" t="n"/>
-      <c r="V57" s="3" t="n"/>
-      <c r="W57" s="3" t="n"/>
-      <c r="X57" s="3" t="n"/>
-      <c r="Y57" s="3" t="n"/>
-      <c r="Z57" s="3" t="n"/>
-      <c r="AA57" s="3" t="n"/>
-      <c r="AB57" s="3" t="n"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8786,14 +11778,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U58" s="3" t="n"/>
-      <c r="V58" s="3" t="n"/>
-      <c r="W58" s="3" t="n"/>
-      <c r="X58" s="3" t="n"/>
-      <c r="Y58" s="3" t="n"/>
-      <c r="Z58" s="3" t="n"/>
-      <c r="AA58" s="3" t="n"/>
-      <c r="AB58" s="3" t="n"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8856,14 +11874,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U59" s="3" t="n"/>
-      <c r="V59" s="3" t="n"/>
-      <c r="W59" s="3" t="n"/>
-      <c r="X59" s="3" t="n"/>
-      <c r="Y59" s="3" t="n"/>
-      <c r="Z59" s="3" t="n"/>
-      <c r="AA59" s="3" t="n"/>
-      <c r="AB59" s="3" t="n"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8926,14 +11970,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U60" s="3" t="n"/>
-      <c r="V60" s="3" t="n"/>
-      <c r="W60" s="3" t="n"/>
-      <c r="X60" s="3" t="n"/>
-      <c r="Y60" s="3" t="n"/>
-      <c r="Z60" s="3" t="n"/>
-      <c r="AA60" s="3" t="n"/>
-      <c r="AB60" s="3" t="n"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8996,14 +12066,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U61" s="3" t="n"/>
-      <c r="V61" s="3" t="n"/>
-      <c r="W61" s="3" t="n"/>
-      <c r="X61" s="3" t="n"/>
-      <c r="Y61" s="3" t="n"/>
-      <c r="Z61" s="3" t="n"/>
-      <c r="AA61" s="3" t="n"/>
-      <c r="AB61" s="3" t="n"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9066,14 +12162,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U62" s="3" t="n"/>
-      <c r="V62" s="3" t="n"/>
-      <c r="W62" s="3" t="n"/>
-      <c r="X62" s="3" t="n"/>
-      <c r="Y62" s="3" t="n"/>
-      <c r="Z62" s="3" t="n"/>
-      <c r="AA62" s="3" t="n"/>
-      <c r="AB62" s="3" t="n"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9136,14 +12258,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U63" s="3" t="n"/>
-      <c r="V63" s="3" t="n"/>
-      <c r="W63" s="3" t="n"/>
-      <c r="X63" s="3" t="n"/>
-      <c r="Y63" s="3" t="n"/>
-      <c r="Z63" s="3" t="n"/>
-      <c r="AA63" s="3" t="n"/>
-      <c r="AB63" s="3" t="n"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Y63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9206,14 +12354,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U64" s="3" t="n"/>
-      <c r="V64" s="3" t="n"/>
-      <c r="W64" s="3" t="n"/>
-      <c r="X64" s="3" t="n"/>
-      <c r="Y64" s="3" t="n"/>
-      <c r="Z64" s="3" t="n"/>
-      <c r="AA64" s="3" t="n"/>
-      <c r="AB64" s="3" t="n"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9276,14 +12450,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U65" s="3" t="n"/>
-      <c r="V65" s="3" t="n"/>
-      <c r="W65" s="3" t="n"/>
-      <c r="X65" s="3" t="n"/>
-      <c r="Y65" s="3" t="n"/>
-      <c r="Z65" s="3" t="n"/>
-      <c r="AA65" s="3" t="n"/>
-      <c r="AB65" s="3" t="n"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="Y65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA65" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB65" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9346,14 +12546,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U66" s="3" t="n"/>
-      <c r="V66" s="3" t="n"/>
-      <c r="W66" s="3" t="n"/>
-      <c r="X66" s="3" t="n"/>
-      <c r="Y66" s="3" t="n"/>
-      <c r="Z66" s="3" t="n"/>
-      <c r="AA66" s="3" t="n"/>
-      <c r="AB66" s="3" t="n"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9416,14 +12642,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U67" s="3" t="n"/>
-      <c r="V67" s="3" t="n"/>
-      <c r="W67" s="3" t="n"/>
-      <c r="X67" s="3" t="n"/>
-      <c r="Y67" s="3" t="n"/>
-      <c r="Z67" s="3" t="n"/>
-      <c r="AA67" s="3" t="n"/>
-      <c r="AB67" s="3" t="n"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9486,14 +12738,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U68" s="3" t="n"/>
-      <c r="V68" s="3" t="n"/>
-      <c r="W68" s="3" t="n"/>
-      <c r="X68" s="3" t="n"/>
-      <c r="Y68" s="3" t="n"/>
-      <c r="Z68" s="3" t="n"/>
-      <c r="AA68" s="3" t="n"/>
-      <c r="AB68" s="3" t="n"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9556,14 +12834,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U69" s="3" t="n"/>
-      <c r="V69" s="3" t="n"/>
-      <c r="W69" s="3" t="n"/>
-      <c r="X69" s="3" t="n"/>
-      <c r="Y69" s="3" t="n"/>
-      <c r="Z69" s="3" t="n"/>
-      <c r="AA69" s="3" t="n"/>
-      <c r="AB69" s="3" t="n"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9626,14 +12930,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U70" s="3" t="n"/>
-      <c r="V70" s="3" t="n"/>
-      <c r="W70" s="3" t="n"/>
-      <c r="X70" s="3" t="n"/>
-      <c r="Y70" s="3" t="n"/>
-      <c r="Z70" s="3" t="n"/>
-      <c r="AA70" s="3" t="n"/>
-      <c r="AB70" s="3" t="n"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W70" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9696,14 +13026,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U71" s="3" t="n"/>
-      <c r="V71" s="3" t="n"/>
-      <c r="W71" s="3" t="n"/>
-      <c r="X71" s="3" t="n"/>
-      <c r="Y71" s="3" t="n"/>
-      <c r="Z71" s="3" t="n"/>
-      <c r="AA71" s="3" t="n"/>
-      <c r="AB71" s="3" t="n"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9766,14 +13122,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U72" s="3" t="n"/>
-      <c r="V72" s="3" t="n"/>
-      <c r="W72" s="3" t="n"/>
-      <c r="X72" s="3" t="n"/>
-      <c r="Y72" s="3" t="n"/>
-      <c r="Z72" s="3" t="n"/>
-      <c r="AA72" s="3" t="n"/>
-      <c r="AB72" s="3" t="n"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9836,14 +13218,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U73" s="3" t="n"/>
-      <c r="V73" s="3" t="n"/>
-      <c r="W73" s="3" t="n"/>
-      <c r="X73" s="3" t="n"/>
-      <c r="Y73" s="3" t="n"/>
-      <c r="Z73" s="3" t="n"/>
-      <c r="AA73" s="3" t="n"/>
-      <c r="AB73" s="3" t="n"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9906,14 +13314,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U74" s="3" t="n"/>
-      <c r="V74" s="3" t="n"/>
-      <c r="W74" s="3" t="n"/>
-      <c r="X74" s="3" t="n"/>
-      <c r="Y74" s="3" t="n"/>
-      <c r="Z74" s="3" t="n"/>
-      <c r="AA74" s="3" t="n"/>
-      <c r="AB74" s="3" t="n"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9976,14 +13410,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U75" s="3" t="n"/>
-      <c r="V75" s="3" t="n"/>
-      <c r="W75" s="3" t="n"/>
-      <c r="X75" s="3" t="n"/>
-      <c r="Y75" s="3" t="n"/>
-      <c r="Z75" s="3" t="n"/>
-      <c r="AA75" s="3" t="n"/>
-      <c r="AB75" s="3" t="n"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10046,14 +13506,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U76" s="3" t="n"/>
-      <c r="V76" s="3" t="n"/>
-      <c r="W76" s="3" t="n"/>
-      <c r="X76" s="3" t="n"/>
-      <c r="Y76" s="3" t="n"/>
-      <c r="Z76" s="3" t="n"/>
-      <c r="AA76" s="3" t="n"/>
-      <c r="AB76" s="3" t="n"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10116,14 +13602,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U77" s="3" t="n"/>
-      <c r="V77" s="3" t="n"/>
-      <c r="W77" s="3" t="n"/>
-      <c r="X77" s="3" t="n"/>
-      <c r="Y77" s="3" t="n"/>
-      <c r="Z77" s="3" t="n"/>
-      <c r="AA77" s="3" t="n"/>
-      <c r="AB77" s="3" t="n"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10186,14 +13698,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U78" s="3" t="n"/>
-      <c r="V78" s="3" t="n"/>
-      <c r="W78" s="3" t="n"/>
-      <c r="X78" s="3" t="n"/>
-      <c r="Y78" s="3" t="n"/>
-      <c r="Z78" s="3" t="n"/>
-      <c r="AA78" s="3" t="n"/>
-      <c r="AB78" s="3" t="n"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10256,14 +13794,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U79" s="3" t="n"/>
-      <c r="V79" s="3" t="n"/>
-      <c r="W79" s="3" t="n"/>
-      <c r="X79" s="3" t="n"/>
-      <c r="Y79" s="3" t="n"/>
-      <c r="Z79" s="3" t="n"/>
-      <c r="AA79" s="3" t="n"/>
-      <c r="AB79" s="3" t="n"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10326,14 +13890,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U80" s="3" t="n"/>
-      <c r="V80" s="3" t="n"/>
-      <c r="W80" s="3" t="n"/>
-      <c r="X80" s="3" t="n"/>
-      <c r="Y80" s="3" t="n"/>
-      <c r="Z80" s="3" t="n"/>
-      <c r="AA80" s="3" t="n"/>
-      <c r="AB80" s="3" t="n"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10396,14 +13986,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U81" s="3" t="n"/>
-      <c r="V81" s="3" t="n"/>
-      <c r="W81" s="3" t="n"/>
-      <c r="X81" s="3" t="n"/>
-      <c r="Y81" s="3" t="n"/>
-      <c r="Z81" s="3" t="n"/>
-      <c r="AA81" s="3" t="n"/>
-      <c r="AB81" s="3" t="n"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10466,14 +14082,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U82" s="3" t="n"/>
-      <c r="V82" s="3" t="n"/>
-      <c r="W82" s="3" t="n"/>
-      <c r="X82" s="3" t="n"/>
-      <c r="Y82" s="3" t="n"/>
-      <c r="Z82" s="3" t="n"/>
-      <c r="AA82" s="3" t="n"/>
-      <c r="AB82" s="3" t="n"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10536,14 +14178,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U83" s="3" t="n"/>
-      <c r="V83" s="3" t="n"/>
-      <c r="W83" s="3" t="n"/>
-      <c r="X83" s="3" t="n"/>
-      <c r="Y83" s="3" t="n"/>
-      <c r="Z83" s="3" t="n"/>
-      <c r="AA83" s="3" t="n"/>
-      <c r="AB83" s="3" t="n"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10606,14 +14274,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U84" s="3" t="n"/>
-      <c r="V84" s="3" t="n"/>
-      <c r="W84" s="3" t="n"/>
-      <c r="X84" s="3" t="n"/>
-      <c r="Y84" s="3" t="n"/>
-      <c r="Z84" s="3" t="n"/>
-      <c r="AA84" s="3" t="n"/>
-      <c r="AB84" s="3" t="n"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10676,14 +14370,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U85" s="3" t="n"/>
-      <c r="V85" s="3" t="n"/>
-      <c r="W85" s="3" t="n"/>
-      <c r="X85" s="3" t="n"/>
-      <c r="Y85" s="3" t="n"/>
-      <c r="Z85" s="3" t="n"/>
-      <c r="AA85" s="3" t="n"/>
-      <c r="AB85" s="3" t="n"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10746,14 +14466,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U86" s="3" t="n"/>
-      <c r="V86" s="3" t="n"/>
-      <c r="W86" s="3" t="n"/>
-      <c r="X86" s="3" t="n"/>
-      <c r="Y86" s="3" t="n"/>
-      <c r="Z86" s="3" t="n"/>
-      <c r="AA86" s="3" t="n"/>
-      <c r="AB86" s="3" t="n"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10816,14 +14562,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U87" s="3" t="n"/>
-      <c r="V87" s="3" t="n"/>
-      <c r="W87" s="3" t="n"/>
-      <c r="X87" s="3" t="n"/>
-      <c r="Y87" s="3" t="n"/>
-      <c r="Z87" s="3" t="n"/>
-      <c r="AA87" s="3" t="n"/>
-      <c r="AB87" s="3" t="n"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10886,14 +14658,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U88" s="3" t="n"/>
-      <c r="V88" s="3" t="n"/>
-      <c r="W88" s="3" t="n"/>
-      <c r="X88" s="3" t="n"/>
-      <c r="Y88" s="3" t="n"/>
-      <c r="Z88" s="3" t="n"/>
-      <c r="AA88" s="3" t="n"/>
-      <c r="AB88" s="3" t="n"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10956,14 +14754,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U89" s="3" t="n"/>
-      <c r="V89" s="3" t="n"/>
-      <c r="W89" s="3" t="n"/>
-      <c r="X89" s="3" t="n"/>
-      <c r="Y89" s="3" t="n"/>
-      <c r="Z89" s="3" t="n"/>
-      <c r="AA89" s="3" t="n"/>
-      <c r="AB89" s="3" t="n"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11026,14 +14850,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U90" s="3" t="n"/>
-      <c r="V90" s="3" t="n"/>
-      <c r="W90" s="3" t="n"/>
-      <c r="X90" s="3" t="n"/>
-      <c r="Y90" s="3" t="n"/>
-      <c r="Z90" s="3" t="n"/>
-      <c r="AA90" s="3" t="n"/>
-      <c r="AB90" s="3" t="n"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11096,14 +14946,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U91" s="3" t="n"/>
-      <c r="V91" s="3" t="n"/>
-      <c r="W91" s="3" t="n"/>
-      <c r="X91" s="3" t="n"/>
-      <c r="Y91" s="3" t="n"/>
-      <c r="Z91" s="3" t="n"/>
-      <c r="AA91" s="3" t="n"/>
-      <c r="AB91" s="3" t="n"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11166,14 +15042,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U92" s="3" t="n"/>
-      <c r="V92" s="3" t="n"/>
-      <c r="W92" s="3" t="n"/>
-      <c r="X92" s="3" t="n"/>
-      <c r="Y92" s="3" t="n"/>
-      <c r="Z92" s="3" t="n"/>
-      <c r="AA92" s="3" t="n"/>
-      <c r="AB92" s="3" t="n"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11236,14 +15138,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U93" s="3" t="n"/>
-      <c r="V93" s="3" t="n"/>
-      <c r="W93" s="3" t="n"/>
-      <c r="X93" s="3" t="n"/>
-      <c r="Y93" s="3" t="n"/>
-      <c r="Z93" s="3" t="n"/>
-      <c r="AA93" s="3" t="n"/>
-      <c r="AB93" s="3" t="n"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11306,14 +15234,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U94" s="3" t="n"/>
-      <c r="V94" s="3" t="n"/>
-      <c r="W94" s="3" t="n"/>
-      <c r="X94" s="3" t="n"/>
-      <c r="Y94" s="3" t="n"/>
-      <c r="Z94" s="3" t="n"/>
-      <c r="AA94" s="3" t="n"/>
-      <c r="AB94" s="3" t="n"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="U94" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA94" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB94" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11376,14 +15330,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U95" s="3" t="n"/>
-      <c r="V95" s="3" t="n"/>
-      <c r="W95" s="3" t="n"/>
-      <c r="X95" s="3" t="n"/>
-      <c r="Y95" s="3" t="n"/>
-      <c r="Z95" s="3" t="n"/>
-      <c r="AA95" s="3" t="n"/>
-      <c r="AB95" s="3" t="n"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="U95" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X95" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA95" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB95" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11446,14 +15426,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U96" s="3" t="n"/>
-      <c r="V96" s="3" t="n"/>
-      <c r="W96" s="3" t="n"/>
-      <c r="X96" s="3" t="n"/>
-      <c r="Y96" s="3" t="n"/>
-      <c r="Z96" s="3" t="n"/>
-      <c r="AA96" s="3" t="n"/>
-      <c r="AB96" s="3" t="n"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="U96" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X96" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA96" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB96" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11516,14 +15522,40 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U97" s="3" t="n"/>
-      <c r="V97" s="3" t="n"/>
-      <c r="W97" s="3" t="n"/>
-      <c r="X97" s="3" t="n"/>
-      <c r="Y97" s="3" t="n"/>
-      <c r="Z97" s="3" t="n"/>
-      <c r="AA97" s="3" t="n"/>
-      <c r="AB97" s="3" t="n"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="U97" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X97" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y97" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z97" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA97" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB97" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14114,14 +18146,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
